--- a/data/xlsx/sbce_config_kvm_ems1_sbce1_template.xlsx
+++ b/data/xlsx/sbce_config_kvm_ems1_sbce1_template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="EMS1" sheetId="1" state="visible" r:id="rId3"/>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">Time Zone - Time Zone in which device is located  (for example America/Edmonton)</t>
   </si>
   <si>
-    <t xml:space="preserve">ntpservers</t>
+    <t xml:space="preserve">ntpserver</t>
   </si>
   <si>
     <t xml:space="preserve">NTP Server Address: - The IPv4 address for NTP servers.</t>
@@ -1519,23 +1519,23 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
-      <formula1>#REF!="ESXI"</formula1>
+      <formula1>#ref!="ESXI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B31:B32" type="custom">
-      <formula1>#REF!&lt;&gt;"EMS+SBCE"</formula1>
+      <formula1>#ref!&lt;&gt;"EMS+SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
-      <formula1>#REF!&lt;&gt;"SBCE"</formula1>
+      <formula1>#ref!&lt;&gt;"SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42 B46:B47" type="custom">
-      <formula1>#REF!&lt;&gt;"EMS"</formula1>
+      <formula1>#ref!&lt;&gt;"EMS"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
-      <formula1>#REF!="SBCE"</formula1>
+      <formula1>#ref!="SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2 B14 B48:B49" type="none">
@@ -2207,19 +2207,19 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
-      <formula1>#REF!="ESXI"</formula1>
+      <formula1>#ref!="ESXI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B31:B32" type="custom">
-      <formula1>#REF!&lt;&gt;"EMS+SBCE"</formula1>
+      <formula1>#ref!&lt;&gt;"EMS+SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
-      <formula1>#REF!&lt;&gt;"SBCE"</formula1>
+      <formula1>#ref!&lt;&gt;"SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
-      <formula1>#REF!="SBCE"</formula1>
+      <formula1>#ref!="SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2 B14 B48:B49" type="none">
@@ -2235,7 +2235,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B46:B47" type="custom">
-      <formula1>#REF!&lt;&gt;"EMS"</formula1>
+      <formula1>#ref!&lt;&gt;"EMS"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
